--- a/public/templates/bulk-email-template.xlsx
+++ b/public/templates/bulk-email-template.xlsx
@@ -27,12 +27,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="009AA0A6"/>
+      <color rgb="FF9AA0A6"/>
     </font>
   </fonts>
   <fills count="4">
@@ -44,12 +43,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000254A"/>
+        <fgColor rgb="FF00254A"/>
+        <bgColor rgb="FF00254A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002CA01C"/>
+        <fgColor rgb="FF2CA01C"/>
+        <bgColor rgb="FF2CA01C"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,16 +66,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -154,19 +154,19 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>QB Enterprise</author>
+    <author>QuickBooks Enterprise</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>Optional
-Shown as 'Company name:' in the email. Falls back to the customer's name if blank.</t>
+Shown as ‘Company name:’ in the email. Falls back to the customer’s name if blank.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>Optional
-Used in the greeting: 'Hi {First Name},'</t>
+Used in the greeting: ‘Hi {First Name},’</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
@@ -190,22 +190,28 @@
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED
-REQUIRED. Shown as 'Affected subscriptions:', e.g. QuickBooks Enterprise Silver Edition</t>
+REQUIRED. Format YYYY-MM-DD, e.g. 2026-09-14. Shown in the email as ‘Next due date:’ — when this subscription is next charged.</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
+        <t>REQUIRED
+REQUIRED. Shown as ‘Affected subscriptions:’, e.g. QuickBooks Enterprise Silver Edition</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
         <t>Optional
-Shown as 'Payment method:', e.g. VISA ending in 1234. Defaults to 'the payment method on file'.</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+Shown as ‘Payment method:’, e.g. VISA ending in 1234. Defaults to ‘the payment method on file’.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Optional
 Reference only — not shown in reminder emails.</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>Optional
 Reference only — not shown in reminder emails.</t>
@@ -504,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -513,13 +519,14 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Company Name</t>
@@ -552,20 +559,25 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Current Payment method</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>License Number</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
@@ -592,7 +604,7 @@
           <t>jane@acme.com</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="3" t="n">
         <v>349.89</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -602,20 +614,25 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>QuickBooks Enterprise Silver Edition</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>VISA ending in 1234</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>1234-5678-9012-345</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>CAN-00417</t>
         </is>

--- a/public/templates/bulk-email-template.xlsx
+++ b/public/templates/bulk-email-template.xlsx
@@ -184,34 +184,28 @@
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED
-REQUIRED. Format YYYY-MM-DD, e.g. 2026-09-07. Cancellation date is auto-set to the next day.</t>
+REQUIRED. Format YYYY-MM-DD, e.g. 2026-09-14. Shown in the email as ‘Due date:’ — when this subscription is next charged. Cancellation date is auto-set to the day after.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>REQUIRED
-REQUIRED. Format YYYY-MM-DD, e.g. 2026-09-14. Shown in the email as ‘Next due date:’ — when this subscription is next charged.</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED
 REQUIRED. Shown as ‘Affected subscriptions:’, e.g. QuickBooks Enterprise Silver Edition</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>Optional
 Shown as ‘Payment method:’, e.g. VISA ending in 1234. Defaults to ‘the payment method on file’.</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Optional
 Reference only — not shown in reminder emails.</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Optional
 Reference only — not shown in reminder emails.</t>
@@ -510,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -519,11 +513,10 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,30 +547,25 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Billing Date</t>
+          <t>Due Date</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Due Date</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
           <t>Product</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Current Payment method</t>
+        </is>
+      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Current Payment method</t>
+          <t>License Number</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>License Number</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
@@ -609,30 +597,25 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>QuickBooks Enterprise Silver Edition</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>QuickBooks Enterprise Silver Edition</t>
+          <t>VISA ending in 1234</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>VISA ending in 1234</t>
+          <t>1234-5678-9012-345</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>1234-5678-9012-345</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>CAN-00417</t>
         </is>

--- a/public/templates/bulk-email-template.xlsx
+++ b/public/templates/bulk-email-template.xlsx
@@ -184,28 +184,34 @@
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED
-REQUIRED. Format YYYY-MM-DD, e.g. 2026-09-14. Shown in the email as ‘Due date:’ — when this subscription is next charged. Cancellation date is auto-set to the day after.</t>
+REQUIRED. Format YYYY-MM-DD, e.g. 2026-09-14. Shown in the email as ‘Due date:’ — when this subscription is next charged.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>REQUIRED
+REQUIRED. Format YYYY-MM-DD, e.g. 2026-09-15. Shown in the email as ‘Cancellation date:’ — when the subscription cancels if payment isn’t fixed. Set this yourself; it is no longer auto-calculated.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED
 REQUIRED. Shown as ‘Affected subscriptions:’, e.g. QuickBooks Enterprise Silver Edition</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Optional
 Shown as ‘Payment method:’, e.g. VISA ending in 1234. Defaults to ‘the payment method on file’.</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Optional
 Reference only — not shown in reminder emails.</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>Optional
 Reference only — not shown in reminder emails.</t>
@@ -504,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -513,10 +519,11 @@
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -552,20 +559,25 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>Cancellation Date</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Current Payment method</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>License Number</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
@@ -602,20 +614,25 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>QuickBooks Enterprise Silver Edition</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>VISA ending in 1234</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>1234-5678-9012-345</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>CAN-00417</t>
         </is>

--- a/public/templates/bulk-email-template.xlsx
+++ b/public/templates/bulk-email-template.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Recipients" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Lists" sheetId="2" state="hidden" r:id="rIdLists"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -196,7 +197,7 @@
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED
-REQUIRED. Shown as ‘Affected subscriptions:’, e.g. QuickBooks Enterprise Silver Edition</t>
+REQUIRED. Pick from the dropdown — typed text that doesn't match a listed product will be skipped when sending. Shown as ‘Affected subscriptions:’.</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
@@ -639,7 +640,153 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid product" error="Please choose a product from the dropdown list, or the row will be skipped when sending." sqref="H2:H1000">
+      <formula1>Lists!$A$1:$A$19</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A19"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>QuickBooks Enterprise Silver Edition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>QuickBooks Enterprise Gold Edition</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QuickBooks Enterprise Platinum Edition</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>QuickBooks Enterprise Diamond Edition</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>QuickBooks Enterprise FSP Edition</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Strategic Mobile Consulting</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mobile Application Porting</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Technology Outsourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UI/UX Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ecommerce App Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Startup app development</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Custom CRM Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SaaS App Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Offshore Development Center</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Product Engineering Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IT Staff Augmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Dedicated Development Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>QuickBooks Payroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Outstanding Balance Payment</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/public/templates/bulk-email-template.xlsx
+++ b/public/templates/bulk-email-template.xlsx
@@ -185,13 +185,13 @@
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED
-REQUIRED. Format YYYY-MM-DD, e.g. 2026-09-14. Shown in the email as ‘Due date:’ — when this subscription is next charged.</t>
+REQUIRED. Format MM/DD/YYYY, e.g. 09/14/2026. Shown in the email as ‘Due date:’ — when this subscription is next charged.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED
-REQUIRED. Format YYYY-MM-DD, e.g. 2026-09-15. Shown in the email as ‘Cancellation date:’ — when the subscription cancels if payment isn’t fixed. Set this yourself; it is no longer auto-calculated.</t>
+REQUIRED. Format MM/DD/YYYY, e.g. 09/15/2026. Shown in the email as ‘Cancellation date:’ — when the subscription cancels if payment isn’t fixed. Set this yourself; it is no longer auto-calculated.</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
@@ -610,12 +610,12 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>09/14/2026</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>09/15/2026</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
